--- a/data/B24_department_schedules_finals/Gıda Mühendisliği.xlsx
+++ b/data/B24_department_schedules_finals/Gıda Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_finals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24FEE18-645D-439C-86F8-DA8FB8575906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{E24FEE18-645D-439C-86F8-DA8FB8575906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89792B4E-6AC9-4E0A-A910-0DC52735E227}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="85">
   <si>
     <t>Year:</t>
   </si>
@@ -266,6 +266,15 @@
   </si>
   <si>
     <t>CAD1,YLAB 1,YLAB 2</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>timeslots</t>
   </si>
 </sst>
 </file>
@@ -346,7 +355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -363,11 +372,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -445,16 +461,21 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{444403B7-CE2B-416B-BDEB-10C8B226D4BA}" name="Table1" displayName="Table1" ref="A1:F36" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
-  <autoFilter ref="A1:F36" xr:uid="{444403B7-CE2B-416B-BDEB-10C8B226D4BA}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F8359D36-C8F6-4B9D-961F-B72A7EBF6203}" name="Year:" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{8FB1CECD-557E-49A7-A277-ACABF42D08FC}" name="Course ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{65B09310-13CA-47B1-B491-5DB0B33B6C9D}" name="Date" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{F1F08436-8A2E-4EB3-BAC1-535E5E76BFDE}" name="Rooms" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{094A7CC3-F368-4375-8D61-1F1DE3026776}" name="Course Name" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{8CD22392-02FE-44AD-AF3D-8F2CCABD189B}" name="Rooms Used" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{444403B7-CE2B-416B-BDEB-10C8B226D4BA}" name="Table1" displayName="Table1" ref="A1:G36" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G36" xr:uid="{444403B7-CE2B-416B-BDEB-10C8B226D4BA}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{F8359D36-C8F6-4B9D-961F-B72A7EBF6203}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{8FB1CECD-557E-49A7-A277-ACABF42D08FC}" name="Course ID" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{65B09310-13CA-47B1-B491-5DB0B33B6C9D}" name="Date" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{F1F08436-8A2E-4EB3-BAC1-535E5E76BFDE}" name="Rooms" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{094A7CC3-F368-4375-8D61-1F1DE3026776}" name="Course Name" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{8CD22392-02FE-44AD-AF3D-8F2CCABD189B}" name="Rooms Used" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{04E3CE6F-077A-4D4D-8B60-2BF8F61F5C92}" name="timeslots" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -747,15 +768,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="46.26953125" customWidth="1"/>
-    <col min="6" max="6" width="42.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="46.265625" customWidth="1"/>
+    <col min="6" max="6" width="42.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,8 +795,17 @@
       <c r="F1" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -794,8 +824,17 @@
       <c r="F2" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2" s="7">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -814,8 +853,17 @@
       <c r="F3" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -834,8 +882,17 @@
       <c r="F4" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" s="7">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -854,8 +911,17 @@
       <c r="F5" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -874,8 +940,14 @@
       <c r="F6" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" s="7">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -894,8 +966,17 @@
       <c r="F7" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" s="7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -914,8 +995,17 @@
       <c r="F8" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -934,8 +1024,17 @@
       <c r="F9" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -954,8 +1053,17 @@
       <c r="F10" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" s="7">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -974,8 +1082,11 @@
       <c r="F11" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -994,8 +1105,11 @@
       <c r="F12" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -1014,8 +1128,11 @@
       <c r="F13" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>2</v>
       </c>
@@ -1034,8 +1151,11 @@
       <c r="F14" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1054,8 +1174,11 @@
       <c r="F15" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>2</v>
       </c>
@@ -1074,8 +1197,11 @@
       <c r="F16" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
         <v>2</v>
       </c>
@@ -1094,8 +1220,11 @@
       <c r="F17" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -1114,8 +1243,11 @@
       <c r="F18" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1134,8 +1266,11 @@
       <c r="F19" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>3</v>
       </c>
@@ -1154,8 +1289,11 @@
       <c r="F20" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>3</v>
       </c>
@@ -1174,8 +1312,11 @@
       <c r="F21" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>3</v>
       </c>
@@ -1194,8 +1335,11 @@
       <c r="F22" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="4">
         <v>3</v>
       </c>
@@ -1214,8 +1358,11 @@
       <c r="F23" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="4">
         <v>3</v>
       </c>
@@ -1234,8 +1381,11 @@
       <c r="F24" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="4">
         <v>3</v>
       </c>
@@ -1254,8 +1404,11 @@
       <c r="F25" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="4">
         <v>3</v>
       </c>
@@ -1274,8 +1427,11 @@
       <c r="F26" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G26" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>4</v>
       </c>
@@ -1294,8 +1450,11 @@
       <c r="F27" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G27" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <v>4</v>
       </c>
@@ -1314,8 +1473,11 @@
       <c r="F28" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G28" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>4</v>
       </c>
@@ -1334,8 +1496,11 @@
       <c r="F29" s="5" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G29" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -1354,8 +1519,11 @@
       <c r="F30" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G30" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5">
         <v>4</v>
       </c>
@@ -1374,8 +1542,11 @@
       <c r="F31" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G31" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5">
         <v>4</v>
       </c>
@@ -1394,8 +1565,11 @@
       <c r="F32" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="5">
         <v>4</v>
       </c>
@@ -1414,8 +1588,11 @@
       <c r="F33" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G33" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="5">
         <v>4</v>
       </c>
@@ -1434,8 +1611,11 @@
       <c r="F34" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G34" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="5">
         <v>4</v>
       </c>
@@ -1454,8 +1634,11 @@
       <c r="F35" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G35" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="5">
         <v>4</v>
       </c>
@@ -1473,6 +1656,9 @@
       </c>
       <c r="F36" s="5" t="s">
         <v>76</v>
+      </c>
+      <c r="G36" s="7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
